--- a/Grupos_Poupanca.xlsx
+++ b/Grupos_Poupanca.xlsx
@@ -1329,13 +1329,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27CDA95B-9248-4199-AAF7-C8AB18395BA8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9C768A1-C962-48AA-A91B-D42FBF89D975}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0511717B-BF8C-4894-97CD-5D3658CB7CF7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF5D045B-4E4C-4624-AB5C-FF8C4ED23C29}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{745CA384-F622-48B6-B26B-60D17CBCEDCF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56A35A2F-2312-44DF-AB12-C778581F02DF}"/>
 </file>
--- a/Grupos_Poupanca.xlsx
+++ b/Grupos_Poupanca.xlsx
@@ -1329,13 +1329,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9C768A1-C962-48AA-A91B-D42FBF89D975}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A632EACB-EDFD-4844-95B7-F35BDA013D6E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF5D045B-4E4C-4624-AB5C-FF8C4ED23C29}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61701A6F-B506-40DE-9772-65232643143B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56A35A2F-2312-44DF-AB12-C778581F02DF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FF043C4-9720-4E60-9132-7942ADB20CEA}"/>
 </file>
--- a/Grupos_Poupanca.xlsx
+++ b/Grupos_Poupanca.xlsx
@@ -1329,13 +1329,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A632EACB-EDFD-4844-95B7-F35BDA013D6E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16548964-9C4B-4426-8651-7B0CBC1F434B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61701A6F-B506-40DE-9772-65232643143B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81AC01C3-DA31-4A86-BEE6-3A8349392062}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FF043C4-9720-4E60-9132-7942ADB20CEA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA164F1C-563E-4862-A668-3370BFFB42F1}"/>
 </file>
--- a/Grupos_Poupanca.xlsx
+++ b/Grupos_Poupanca.xlsx
@@ -1329,13 +1329,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16548964-9C4B-4426-8651-7B0CBC1F434B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4422C438-8FFE-4B0A-90F9-D1E43371CC0E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81AC01C3-DA31-4A86-BEE6-3A8349392062}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5C6795C-645A-4E57-971E-B79F371C889C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA164F1C-563E-4862-A668-3370BFFB42F1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D70CABC2-E6ED-47F6-AB45-2177D8285F42}"/>
 </file>
--- a/Grupos_Poupanca.xlsx
+++ b/Grupos_Poupanca.xlsx
@@ -1329,13 +1329,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4422C438-8FFE-4B0A-90F9-D1E43371CC0E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A2D88A4-B442-467A-B503-E39E8722FAF0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5C6795C-645A-4E57-971E-B79F371C889C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCF8ACDE-B052-4049-8553-3D3DDB171853}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D70CABC2-E6ED-47F6-AB45-2177D8285F42}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBF60A36-766E-4B17-9060-2DA14A0DBF45}"/>
 </file>